--- a/data/trans_orig/P16A12-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14712</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>34103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39364</t>
+          <t>41343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440549</t>
+          <t>439673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459064</t>
+          <t>458592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295551</t>
+          <t>295146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304852</t>
+          <t>304875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741093</t>
+          <t>739114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>761962</t>
+          <t>760749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>33205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342162</t>
+          <t>341952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356816</t>
+          <t>357348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359364</t>
+          <t>359748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369822</t>
+          <t>369866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>706220</t>
+          <t>705594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724749</t>
+          <t>724367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40367</t>
+          <t>38790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53660</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502022</t>
+          <t>503599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523114</t>
+          <t>523528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147476</t>
+          <t>146948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160938</t>
+          <t>160712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656511</t>
+          <t>656318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680309</t>
+          <t>680642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74604</t>
+          <t>75512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112200</t>
+          <t>111991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21591</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43363</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104212</t>
+          <t>103094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145386</t>
+          <t>145490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1126134</t>
+          <t>1126343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1163730</t>
+          <t>1162822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>670922</t>
+          <t>671525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>692694</t>
+          <t>692531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1807234</t>
+          <t>1807130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1848408</t>
+          <t>1849526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>32827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>41092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>39858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>66681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317099</t>
+          <t>316710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335286</t>
+          <t>335498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>525934</t>
+          <t>527660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548882</t>
+          <t>548881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>850390</t>
+          <t>851608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>880155</t>
+          <t>878431</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101145</t>
+          <t>102654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143211</t>
+          <t>143851</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102013</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146871</t>
+          <t>145598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293614</t>
+          <t>293587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1105549</t>
+          <t>1104909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1147615</t>
+          <t>1146106</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1400089</t>
+          <t>1401362</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1444947</t>
+          <t>1443280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159449</t>
+          <t>157786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211810</t>
+          <t>208829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>179170</t>
+          <t>178419</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>234233</t>
+          <t>231603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>350504</t>
+          <t>351079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425708</t>
+          <t>424306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3057362</t>
+          <t>3060343</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3109723</t>
+          <t>3111386</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3143891</t>
+          <t>3146521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3198954</t>
+          <t>3199705</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6221588</t>
+          <t>6222990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6296792</t>
+          <t>6296217</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29331</t>
+          <t>29247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44936</t>
+          <t>45047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407880</t>
+          <t>407964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426138</t>
+          <t>425237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293757</t>
+          <t>292737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308393</t>
+          <t>308422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706729</t>
+          <t>706618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>730087</t>
+          <t>730542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30692</t>
+          <t>33295</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>21286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44808</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386326</t>
+          <t>383723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403273</t>
+          <t>402275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317932</t>
+          <t>318270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331261</t>
+          <t>331370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707525</t>
+          <t>708189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731006</t>
+          <t>731047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50205</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81196</t>
+          <t>81031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65840</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103163</t>
+          <t>99892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547133</t>
+          <t>547298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>578124</t>
+          <t>578060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231757</t>
+          <t>232269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248507</t>
+          <t>248046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>783104</t>
+          <t>786375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820427</t>
+          <t>821392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84606</t>
+          <t>83632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125030</t>
+          <t>124449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52563</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120775</t>
+          <t>120496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167462</t>
+          <t>169882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1032285</t>
+          <t>1032866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1072709</t>
+          <t>1073683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>714094</t>
+          <t>713839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>739048</t>
+          <t>739688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1756511</t>
+          <t>1754091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1803198</t>
+          <t>1803477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>48846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52390</t>
+          <t>53183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82898</t>
+          <t>85054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84740</t>
+          <t>86022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124935</t>
+          <t>124842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463253</t>
+          <t>461750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>486253</t>
+          <t>485849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676407</t>
+          <t>674251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>706915</t>
+          <t>706122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1144966</t>
+          <t>1145059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1185161</t>
+          <t>1183879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132029</t>
+          <t>132334</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176609</t>
+          <t>180203</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135291</t>
+          <t>136576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184467</t>
+          <t>186079</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252409</t>
+          <t>252531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263902</t>
+          <t>263929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>928647</t>
+          <t>925053</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>973227</t>
+          <t>972922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1186631</t>
+          <t>1185019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1235807</t>
+          <t>1234522</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>222650</t>
+          <t>221121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>284519</t>
+          <t>283928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>264424</t>
+          <t>267849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>330724</t>
+          <t>335566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>499680</t>
+          <t>503899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>599141</t>
+          <t>599083</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3131791</t>
+          <t>3132382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3193660</t>
+          <t>3195189</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3208202</t>
+          <t>3203360</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3274502</t>
+          <t>3271077</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6356095</t>
+          <t>6356153</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6455556</t>
+          <t>6451337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44129</t>
+          <t>45116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57818</t>
+          <t>57893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384963</t>
+          <t>383976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407932</t>
+          <t>408100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>325623</t>
+          <t>325430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339962</t>
+          <t>339989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>718329</t>
+          <t>718254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744609</t>
+          <t>744678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>33138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>23196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46519</t>
+          <t>47470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>344089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361983</t>
+          <t>362352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353236</t>
+          <t>352295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367878</t>
+          <t>367727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702981</t>
+          <t>702030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726558</t>
+          <t>726304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>40282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67973</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48811</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80616</t>
+          <t>78835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453941</t>
+          <t>453796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>482579</t>
+          <t>481632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146385</t>
+          <t>146657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160843</t>
+          <t>160774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607420</t>
+          <t>609201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639225</t>
+          <t>639027</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86722</t>
+          <t>86523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126307</t>
+          <t>124797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116115</t>
+          <t>115077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159929</t>
+          <t>162414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1023331</t>
+          <t>1024841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1062916</t>
+          <t>1063115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>782198</t>
+          <t>781650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>805698</t>
+          <t>804725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1815585</t>
+          <t>1813100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1859399</t>
+          <t>1860437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83246</t>
+          <t>82422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,82 +7390,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>67983</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52750</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85261</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>134501</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>115088</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>158530</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67983</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>53317</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>87746</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>134501</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>113002</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>158925</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>537460</t>
+          <t>538284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>568121</t>
+          <t>567718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,82 +7503,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>670261</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>652983</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>685494</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>88,45%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1166</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1224449</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1200420</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1243862</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>91,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>670261</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>650498</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>684927</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1224449</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1200025</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1245948</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>88,31%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123379</t>
+          <t>122888</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169825</t>
+          <t>171396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125150</t>
+          <t>126185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172038</t>
+          <t>176570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277295</t>
+          <t>276380</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286068</t>
+          <t>286009</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>912200</t>
+          <t>910629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>958646</t>
+          <t>959137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1197132</t>
+          <t>1192600</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1244020</t>
+          <t>1242985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>255846</t>
+          <t>251519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>319842</t>
+          <t>312737</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>241726</t>
+          <t>246107</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314529</t>
+          <t>309954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>516352</t>
+          <t>517966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>610851</t>
+          <t>612515</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3065880</t>
+          <t>3072985</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3129876</t>
+          <t>3134203</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3217067</t>
+          <t>3221642</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3289870</t>
+          <t>3285489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6306467</t>
+          <t>6304803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6400966</t>
+          <t>6399352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29450</t>
+          <t>29462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>51844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66600</t>
+          <t>66679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454338</t>
+          <t>453368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>475762</t>
+          <t>475750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426681</t>
+          <t>427398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438020</t>
+          <t>437807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>886079</t>
+          <t>886000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31986</t>
+          <t>32231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55176</t>
+          <t>54761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39861</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63622</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397037</t>
+          <t>397452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420227</t>
+          <t>419982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368112</t>
+          <t>367830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376793</t>
+          <t>376940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771171</t>
+          <t>770587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794932</t>
+          <t>794534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78013</t>
+          <t>77905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>28656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94224</t>
+          <t>93428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590251</t>
+          <t>590359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653206</t>
+          <t>653069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144746</t>
+          <t>144112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155684</t>
+          <t>155265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>740951</t>
+          <t>741747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>809620</t>
+          <t>806519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91316</t>
+          <t>92940</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127614</t>
+          <t>127632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55701</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105563</t>
+          <t>99656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178472</t>
+          <t>177887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907205</t>
+          <t>907187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>943503</t>
+          <t>941879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>921827</t>
+          <t>920468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>956367</t>
+          <t>957669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833875</t>
+          <t>1834460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906784</t>
+          <t>1912691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32211</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>54881</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>62532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102296</t>
+          <t>102456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145619</t>
+          <t>145808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419387</t>
+          <t>419168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>441838</t>
+          <t>441992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>737437</t>
+          <t>739252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>776976</t>
+          <t>776464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1167426</t>
+          <t>1167237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1210749</t>
+          <t>1210589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>72255</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98045</t>
+          <t>98738</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72805</t>
+          <t>73005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99691</t>
+          <t>101203</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233813</t>
+          <t>234430</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240025</t>
+          <t>240026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>662107</t>
+          <t>661414</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>689160</t>
+          <t>687897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>900968</t>
+          <t>899456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>927854</t>
+          <t>927654</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209292</t>
+          <t>216062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>316822</t>
+          <t>317026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>201652</t>
+          <t>203934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>278113</t>
+          <t>277490</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461581</t>
+          <t>454049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>580447</t>
+          <t>579874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3058242</t>
+          <t>3058038</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3165772</t>
+          <t>3159002</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3295521</t>
+          <t>3296144</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3371982</t>
+          <t>3369700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6368250</t>
+          <t>6368823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6487116</t>
+          <t>6494648</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A12-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>39145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439673</t>
+          <t>440348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458592</t>
+          <t>459349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295146</t>
+          <t>295544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304875</t>
+          <t>304885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739114</t>
+          <t>741312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>760749</t>
+          <t>761946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33205</t>
+          <t>30943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341952</t>
+          <t>341402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357348</t>
+          <t>356844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359748</t>
+          <t>359267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369866</t>
+          <t>369942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705594</t>
+          <t>707856</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724367</t>
+          <t>724272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>19789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53853</t>
+          <t>55337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503599</t>
+          <t>503543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523528</t>
+          <t>522600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146948</t>
+          <t>146576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160712</t>
+          <t>160743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656318</t>
+          <t>654834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680642</t>
+          <t>680580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75512</t>
+          <t>75147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111991</t>
+          <t>111639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42760</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103094</t>
+          <t>102174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145490</t>
+          <t>143552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1126343</t>
+          <t>1126695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1162822</t>
+          <t>1163187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671525</t>
+          <t>671933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>692531</t>
+          <t>692806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1807130</t>
+          <t>1809068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1849526</t>
+          <t>1850446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>33089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41092</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>39499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66681</t>
+          <t>68143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>316710</t>
+          <t>316448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335498</t>
+          <t>335312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527660</t>
+          <t>526384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548881</t>
+          <t>549108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851608</t>
+          <t>850146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>878431</t>
+          <t>878790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102654</t>
+          <t>103620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143851</t>
+          <t>142769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103680</t>
+          <t>104714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145598</t>
+          <t>147323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293587</t>
+          <t>293602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1104909</t>
+          <t>1105991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1146106</t>
+          <t>1145140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1401362</t>
+          <t>1399637</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1443280</t>
+          <t>1442246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>157786</t>
+          <t>157677</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208829</t>
+          <t>207883</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178419</t>
+          <t>179925</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231603</t>
+          <t>234873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2841,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>388244</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>351243</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>428348</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>388244</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>351079</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>424306</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3060343</t>
+          <t>3061289</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3111386</t>
+          <t>3111495</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3146521</t>
+          <t>3143251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3199705</t>
+          <t>3198199</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6222990</t>
+          <t>6218948</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6296217</t>
+          <t>6296053</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>21191</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>46638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407964</t>
+          <t>407816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425237</t>
+          <t>426124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>292737</t>
+          <t>293448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308422</t>
+          <t>308434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706618</t>
+          <t>705027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>730542</t>
+          <t>730474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21286</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383723</t>
+          <t>384517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402275</t>
+          <t>403012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318270</t>
+          <t>317920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331370</t>
+          <t>331193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708189</t>
+          <t>709024</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731047</t>
+          <t>731497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>50950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>82760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64875</t>
+          <t>63781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99892</t>
+          <t>101204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547298</t>
+          <t>545569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>578060</t>
+          <t>577379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232269</t>
+          <t>231556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248046</t>
+          <t>248483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>786375</t>
+          <t>785063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>821392</t>
+          <t>822486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83632</t>
+          <t>83216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124449</t>
+          <t>124801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52818</t>
+          <t>55543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120496</t>
+          <t>120712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>168675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1032866</t>
+          <t>1032514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1073683</t>
+          <t>1074099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713839</t>
+          <t>711114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>739688</t>
+          <t>738329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1754091</t>
+          <t>1755298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1803477</t>
+          <t>1803261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>48427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53183</t>
+          <t>51564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85054</t>
+          <t>83929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86022</t>
+          <t>83915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124842</t>
+          <t>122595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461750</t>
+          <t>462169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485849</t>
+          <t>486541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>674251</t>
+          <t>675376</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>706122</t>
+          <t>707741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1145059</t>
+          <t>1147306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183879</t>
+          <t>1185986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132334</t>
+          <t>133795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180203</t>
+          <t>179596</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136576</t>
+          <t>136644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186079</t>
+          <t>185291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252531</t>
+          <t>251827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263929</t>
+          <t>263876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>925053</t>
+          <t>925660</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>972922</t>
+          <t>971461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1185019</t>
+          <t>1185807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1234522</t>
+          <t>1234454</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221121</t>
+          <t>220119</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>283928</t>
+          <t>290195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>267849</t>
+          <t>269439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>335566</t>
+          <t>333320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>503899</t>
+          <t>501314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>599083</t>
+          <t>598584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3132382</t>
+          <t>3126115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3195189</t>
+          <t>3196191</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3203360</t>
+          <t>3205606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3271077</t>
+          <t>3269487</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6356153</t>
+          <t>6356652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6451337</t>
+          <t>6453922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45116</t>
+          <t>44527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>31959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57893</t>
+          <t>59385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383976</t>
+          <t>384565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408100</t>
+          <t>408199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>325430</t>
+          <t>325881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339989</t>
+          <t>340627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>718254</t>
+          <t>716762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744678</t>
+          <t>744188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47470</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344089</t>
+          <t>343720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362352</t>
+          <t>361882</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352295</t>
+          <t>352660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367727</t>
+          <t>367856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702030</t>
+          <t>703851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726304</t>
+          <t>726907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68118</t>
+          <t>68331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49009</t>
+          <t>51022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78835</t>
+          <t>81718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>453583</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481632</t>
+          <t>483163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146657</t>
+          <t>146215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160774</t>
+          <t>160972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609201</t>
+          <t>606318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639027</t>
+          <t>637014</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86523</t>
+          <t>90438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124797</t>
+          <t>128692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>43682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115077</t>
+          <t>114419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162414</t>
+          <t>160879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1024841</t>
+          <t>1020946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1063115</t>
+          <t>1059200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>781650</t>
+          <t>782194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>804725</t>
+          <t>805570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1813100</t>
+          <t>1814635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1860437</t>
+          <t>1861095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52988</t>
+          <t>52343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82422</t>
+          <t>82260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52750</t>
+          <t>52036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85261</t>
+          <t>85347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115088</t>
+          <t>113129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158530</t>
+          <t>159770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538284</t>
+          <t>538446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>567718</t>
+          <t>568363</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>652983</t>
+          <t>652897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>685494</t>
+          <t>686208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1200420</t>
+          <t>1199180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1243862</t>
+          <t>1245821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122888</t>
+          <t>121800</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171396</t>
+          <t>168151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126185</t>
+          <t>124172</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176570</t>
+          <t>174375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276380</t>
+          <t>277747</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286009</t>
+          <t>286023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>910629</t>
+          <t>913874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>959137</t>
+          <t>960225</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1192600</t>
+          <t>1194795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1242985</t>
+          <t>1244998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>251519</t>
+          <t>254791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>312737</t>
+          <t>316682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>246107</t>
+          <t>248411</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>309954</t>
+          <t>314310</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>517966</t>
+          <t>519245</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>612515</t>
+          <t>612017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3072985</t>
+          <t>3069040</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3134203</t>
+          <t>3130931</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3221642</t>
+          <t>3217286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3285489</t>
+          <t>3283185</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6304803</t>
+          <t>6305301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6399352</t>
+          <t>6398073</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>42131</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51844</t>
+          <t>55888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>45005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>69546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>465989</t>
+          <t>508487</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453368</t>
+          <t>494730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>475750</t>
+          <t>517895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>433539</t>
+          <t>473422</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427398</t>
+          <t>466958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>437807</t>
+          <t>478371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>899528</t>
+          <t>981909</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>886000</t>
+          <t>969483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>910729</t>
+          <t>994024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41878</t>
+          <t>42981</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54761</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14750</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>53698</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>41985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64206</t>
+          <t>66864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>410335</t>
+          <t>440231</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397452</t>
+          <t>427860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419982</t>
+          <t>451875</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>373362</t>
+          <t>412426</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367830</t>
+          <t>406700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376940</t>
+          <t>416550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>783697</t>
+          <t>852657</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>770587</t>
+          <t>839491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794534</t>
+          <t>864370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>37439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>60390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>62732</t>
+          <t>66960</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93428</t>
+          <t>82269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>622057</t>
+          <t>423029</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590359</t>
+          <t>411222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653069</t>
+          <t>434173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>150386</t>
+          <t>169120</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144112</t>
+          <t>162718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155265</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>772443</t>
+          <t>592149</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>741747</t>
+          <t>576840</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>806519</t>
+          <t>603780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>108667</t>
+          <t>121562</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92940</t>
+          <t>104181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127632</t>
+          <t>141625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>44883</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57060</t>
+          <t>55005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>4,23%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>149975</t>
+          <t>166445</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99656</t>
+          <t>144762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177887</t>
+          <t>189444</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>926152</t>
+          <t>1010281</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907187</t>
+          <t>990218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>941879</t>
+          <t>1027662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,34 +9810,34 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>936220</t>
+          <t>815732</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>920468</t>
+          <t>805610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>957669</t>
+          <t>824233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>95,77%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2102</t>
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1862372</t>
+          <t>1826013</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1834460</t>
+          <t>1803014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912691</t>
+          <t>1847696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>46299</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32057</t>
+          <t>35051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54881</t>
+          <t>58847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>84229</t>
+          <t>91382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99744</t>
+          <t>105592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,27 +10075,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>126410</t>
+          <t>137680</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102456</t>
+          <t>120876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145808</t>
+          <t>155015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>431868</t>
+          <t>520677</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419168</t>
+          <t>508129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>441992</t>
+          <t>531925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>754767</t>
+          <t>738745</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739252</t>
+          <t>724535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>776464</t>
+          <t>752306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,22 +10188,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1186635</t>
+          <t>1259423</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1167237</t>
+          <t>1242088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1210589</t>
+          <t>1276227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,27 +10348,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84369</t>
+          <t>91483</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72255</t>
+          <t>77558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98738</t>
+          <t>105820</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>86390</t>
+          <t>93497</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73005</t>
+          <t>79403</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101203</t>
+          <t>109036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -10461,22 +10461,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>238486</t>
+          <t>235214</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234430</t>
+          <t>231222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240026</t>
+          <t>236692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>675783</t>
+          <t>751510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>661414</t>
+          <t>737173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>687897</t>
+          <t>765435</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>914269</t>
+          <t>986724</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>899456</t>
+          <t>971185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>927654</t>
+          <t>1000818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>280177</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>216062</t>
+          <t>276570</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>317026</t>
+          <t>335875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>249577</t>
+          <t>271830</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>203934</t>
+          <t>246156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>277490</t>
+          <t>296531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>529754</t>
+          <t>575399</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>454049</t>
+          <t>537713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>579874</t>
+          <t>615713</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3094887</t>
+          <t>3137919</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3058038</t>
+          <t>3105613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3159002</t>
+          <t>3164918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3324057</t>
+          <t>3360956</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3296144</t>
+          <t>3336255</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3369700</t>
+          <t>3386630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6418943</t>
+          <t>6498876</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6368823</t>
+          <t>6458562</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6494648</t>
+          <t>6536562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6948697</t>
+          <t>7074275</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
